--- a/data/trans_dic/P19C03-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C03-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por un empaste</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por un empaste (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,18; 33,77</t>
+          <t>24,15; 33,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,5; 41,13</t>
+          <t>31,18; 41,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,53; 28,97</t>
+          <t>20,05; 29,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,86; 22,79</t>
+          <t>15,0; 23,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,65; 37,93</t>
+          <t>27,46; 38,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,52; 32,78</t>
+          <t>21,61; 32,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,74; 25,67</t>
+          <t>16,56; 25,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,6; 20,53</t>
+          <t>14,19; 20,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,32; 34,16</t>
+          <t>27,12; 34,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,86; 36,57</t>
+          <t>28,67; 36,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,52; 25,81</t>
+          <t>19,57; 25,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,49; 20,53</t>
+          <t>15,59; 20,46</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,96; 39,02</t>
+          <t>27,62; 39,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,52; 33,2</t>
+          <t>23,43; 32,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,49; 31,49</t>
+          <t>21,45; 31,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 19,48</t>
+          <t>12,23; 19,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,9; 42,38</t>
+          <t>31,85; 41,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,76; 36,22</t>
+          <t>25,13; 35,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,76; 34,12</t>
+          <t>23,7; 34,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,72; 19,59</t>
+          <t>13,68; 19,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,72; 39,16</t>
+          <t>31,77; 39,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,35; 32,64</t>
+          <t>25,13; 32,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,05; 30,95</t>
+          <t>23,93; 31,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,75; 18,69</t>
+          <t>13,63; 18,25</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,67; 39,98</t>
+          <t>30,82; 40,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,48; 33,36</t>
+          <t>25,21; 33,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,88; 34,25</t>
+          <t>25,23; 34,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 22,54</t>
+          <t>5,09; 23,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,92; 39,59</t>
+          <t>24,6; 40,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,69; 36,22</t>
+          <t>24,71; 36,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,0; 33,92</t>
+          <t>18,8; 33,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,75; 21,87</t>
+          <t>11,87; 22,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,66; 38,82</t>
+          <t>30,75; 38,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,15; 33,05</t>
+          <t>26,37; 33,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,73; 32,58</t>
+          <t>24,6; 32,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 21,14</t>
+          <t>5,64; 21,2</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,83; 34,24</t>
+          <t>28,17; 34,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,98; 32,05</t>
+          <t>26,15; 31,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,38; 32,56</t>
+          <t>26,06; 32,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,06; 24,93</t>
+          <t>19,0; 24,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,03; 40,42</t>
+          <t>31,76; 40,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,04; 36,8</t>
+          <t>29,38; 36,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,67; 36,6</t>
+          <t>29,56; 36,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 22,33</t>
+          <t>9,08; 22,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,7; 35,74</t>
+          <t>30,5; 35,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,2; 32,74</t>
+          <t>28,28; 32,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,83; 33,53</t>
+          <t>28,67; 33,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,33; 22,36</t>
+          <t>13,6; 22,37</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,64; 40,15</t>
+          <t>27,42; 39,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,44; 33,07</t>
+          <t>23,95; 32,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,1; 31,72</t>
+          <t>22,64; 31,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,44; 22,59</t>
+          <t>14,44; 22,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,86; 38,96</t>
+          <t>29,84; 38,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,53; 31,03</t>
+          <t>24,4; 31,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,76; 32,48</t>
+          <t>24,98; 32,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,31; 31,11</t>
+          <t>15,46; 31,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,36; 37,82</t>
+          <t>30,14; 37,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,3; 30,77</t>
+          <t>25,38; 30,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,02; 30,83</t>
+          <t>25,21; 30,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,21; 26,84</t>
+          <t>16,59; 28,55</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,55; 37,17</t>
+          <t>24,89; 36,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,66; 39,0</t>
+          <t>26,86; 39,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,19; 32,49</t>
+          <t>20,96; 32,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,91; 27,03</t>
+          <t>8,38; 27,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,01; 29,68</t>
+          <t>24,23; 29,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,4; 30,1</t>
+          <t>24,0; 29,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,91; 22,59</t>
+          <t>17,12; 23,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,24; 17,88</t>
+          <t>12,01; 17,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,14; 30,08</t>
+          <t>24,94; 30,18</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,56; 30,91</t>
+          <t>25,4; 30,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,74; 23,82</t>
+          <t>18,47; 23,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,33; 18,45</t>
+          <t>12,28; 18,42</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,13; 33,94</t>
+          <t>30,22; 34,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,15; 31,8</t>
+          <t>28,27; 31,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,79; 29,38</t>
+          <t>25,8; 29,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,76; 19,92</t>
+          <t>13,76; 20,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,11; 33,79</t>
+          <t>30,3; 33,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,44; 30,72</t>
+          <t>27,5; 30,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,54; 27,77</t>
+          <t>24,51; 27,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,5; 19,87</t>
+          <t>14,62; 19,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,8; 33,38</t>
+          <t>30,58; 33,33</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,38; 30,78</t>
+          <t>28,34; 30,81</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25,6; 28,05</t>
+          <t>25,61; 28,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,19; 19,26</t>
+          <t>15,22; 19,45</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por un empaste</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por un empaste (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93417; 130459</t>
+          <t>93279; 128128</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>124525; 162612</t>
+          <t>123268; 163485</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75713; 112288</t>
+          <t>77707; 113422</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74067; 113615</t>
+          <t>74778; 115441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71498; 101773</t>
+          <t>73680; 104395</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62845; 95716</t>
+          <t>63110; 96262</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52868; 81071</t>
+          <t>52303; 80774</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>64369; 90516</t>
+          <t>62568; 90433</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>178806; 223576</t>
+          <t>177519; 224712</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>198373; 251364</t>
+          <t>197050; 248179</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>137296; 181558</t>
+          <t>137674; 182455</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>145472; 192856</t>
+          <t>146433; 192233</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83925; 117135</t>
+          <t>82905; 119286</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90040; 127094</t>
+          <t>89692; 126061</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68065; 99721</t>
+          <t>67927; 100441</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53562; 87337</t>
+          <t>54863; 89477</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>106424; 141368</t>
+          <t>106231; 140009</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77635; 113547</t>
+          <t>78795; 112508</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79266; 113813</t>
+          <t>79053; 114973</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51799; 73991</t>
+          <t>51641; 74503</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>201019; 248179</t>
+          <t>201349; 248752</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>176522; 227269</t>
+          <t>175011; 226065</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>156368; 201231</t>
+          <t>155611; 201740</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>113564; 154395</t>
+          <t>112600; 150767</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>131970; 172025</t>
+          <t>132615; 173369</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>136426; 178655</t>
+          <t>134999; 179991</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100806; 138775</t>
+          <t>102242; 139349</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30112; 148959</t>
+          <t>33651; 152128</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33504; 55450</t>
+          <t>34452; 56386</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59421; 87177</t>
+          <t>59470; 87806</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26486; 47294</t>
+          <t>26205; 46989</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19386; 36085</t>
+          <t>19590; 36371</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>174869; 221417</t>
+          <t>175401; 220530</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>202975; 256518</t>
+          <t>204684; 258337</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134666; 177460</t>
+          <t>134004; 177531</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55366; 174535</t>
+          <t>46563; 175060</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>242252; 298048</t>
+          <t>245222; 297669</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>252460; 311450</t>
+          <t>254076; 309384</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>232046; 286382</t>
+          <t>229201; 285998</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>190254; 248871</t>
+          <t>189653; 243919</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>191001; 241015</t>
+          <t>189387; 239076</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>202689; 256805</t>
+          <t>205020; 256503</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>202974; 250333</t>
+          <t>202197; 252827</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>91195; 214089</t>
+          <t>87087; 216223</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>450294; 524240</t>
+          <t>447324; 520573</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>470853; 546720</t>
+          <t>472236; 549121</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>450733; 524318</t>
+          <t>448221; 523279</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>260815; 437503</t>
+          <t>266191; 437854</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>68524; 99536</t>
+          <t>67989; 96989</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94550; 133395</t>
+          <t>96604; 132908</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98221; 134871</t>
+          <t>96266; 132660</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63353; 99143</t>
+          <t>63361; 98077</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>136169; 177677</t>
+          <t>136110; 177003</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>164308; 207826</t>
+          <t>163463; 211783</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>138042; 181052</t>
+          <t>139270; 180803</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>124512; 253058</t>
+          <t>125730; 253907</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>213757; 266260</t>
+          <t>212221; 262348</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>271547; 330233</t>
+          <t>272358; 330846</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>245865; 302963</t>
+          <t>247769; 303961</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>202920; 336049</t>
+          <t>207789; 357559</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52109; 78889</t>
+          <t>52821; 77719</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>58731; 85910</t>
+          <t>59170; 86691</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48762; 78490</t>
+          <t>50639; 78732</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20676; 62738</t>
+          <t>19451; 63818</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>227010; 280619</t>
+          <t>229120; 282085</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>226082; 278845</t>
+          <t>222334; 276224</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>139592; 186444</t>
+          <t>141266; 190744</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>91023; 133021</t>
+          <t>89347; 128645</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>291130; 348320</t>
+          <t>288798; 349448</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>293109; 354487</t>
+          <t>291302; 350945</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>199974; 254158</t>
+          <t>197042; 252752</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>120361; 180041</t>
+          <t>119852; 179740</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>737405; 830551</t>
+          <t>739596; 832776</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>818894; 925199</t>
+          <t>822372; 924117</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>685036; 780318</t>
+          <t>685229; 784126</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>450805; 652680</t>
+          <t>450966; 657423</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>824887; 925822</t>
+          <t>830243; 927306</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>861690; 964865</t>
+          <t>863596; 967388</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>700881; 792990</t>
+          <t>699815; 795236</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>507437; 695305</t>
+          <t>511613; 695988</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1597520; 1731663</t>
+          <t>1586082; 1728662</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1716983; 1861944</t>
+          <t>1714398; 1863697</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1411081; 1545716</t>
+          <t>1411321; 1552632</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1029299; 1305133</t>
+          <t>1031265; 1318217</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C03-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C03-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,15; 33,17</t>
+          <t>24,63; 33,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,18; 41,35</t>
+          <t>31,27; 41,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,05; 29,26</t>
+          <t>19,37; 28,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,0; 23,16</t>
+          <t>13,99; 21,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,46; 38,91</t>
+          <t>26,59; 38,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,61; 32,96</t>
+          <t>21,53; 32,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,56; 25,58</t>
+          <t>16,43; 25,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,19; 20,51</t>
+          <t>14,68; 20,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,12; 34,33</t>
+          <t>26,82; 33,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,67; 36,11</t>
+          <t>28,53; 36,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,57; 25,94</t>
+          <t>19,68; 26,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,59; 20,46</t>
+          <t>15,32; 20,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,62; 39,73</t>
+          <t>28,05; 39,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,43; 32,93</t>
+          <t>22,96; 32,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,45; 31,72</t>
+          <t>20,88; 31,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,23; 19,95</t>
+          <t>12,22; 19,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,85; 41,97</t>
+          <t>32,0; 42,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,13; 35,89</t>
+          <t>25,48; 35,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,7; 34,47</t>
+          <t>23,76; 33,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,68; 19,73</t>
+          <t>14,48; 20,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,77; 39,25</t>
+          <t>31,71; 39,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,13; 32,47</t>
+          <t>25,4; 32,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23,93; 31,03</t>
+          <t>23,9; 31,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,63; 18,25</t>
+          <t>14,05; 19,08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,82; 40,29</t>
+          <t>30,97; 39,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,21; 33,61</t>
+          <t>25,46; 33,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,23; 34,39</t>
+          <t>25,39; 34,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 23,02</t>
+          <t>18,93; 27,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,6; 40,26</t>
+          <t>24,1; 40,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,71; 36,48</t>
+          <t>24,37; 36,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,8; 33,7</t>
+          <t>19,29; 34,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,87; 22,05</t>
+          <t>12,69; 22,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,75; 38,67</t>
+          <t>30,7; 38,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,37; 33,28</t>
+          <t>26,31; 32,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,6; 32,6</t>
+          <t>24,41; 32,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 21,2</t>
+          <t>17,83; 24,68</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,17; 34,2</t>
+          <t>28,22; 34,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,15; 31,84</t>
+          <t>25,83; 31,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,06; 32,52</t>
+          <t>26,08; 32,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,0; 24,44</t>
+          <t>17,97; 23,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,76; 40,1</t>
+          <t>31,95; 39,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,38; 36,75</t>
+          <t>29,35; 36,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,56; 36,96</t>
+          <t>29,65; 36,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,08; 22,55</t>
+          <t>19,23; 24,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,5; 35,49</t>
+          <t>30,56; 35,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,28; 32,89</t>
+          <t>27,83; 32,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,67; 33,47</t>
+          <t>28,61; 33,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,6; 22,37</t>
+          <t>19,03; 22,72</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,42; 39,12</t>
+          <t>28,4; 40,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,95; 32,95</t>
+          <t>23,8; 32,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,64; 31,2</t>
+          <t>23,02; 31,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,44; 22,35</t>
+          <t>16,1; 24,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,84; 38,81</t>
+          <t>29,83; 38,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,4; 31,62</t>
+          <t>24,22; 31,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,98; 32,43</t>
+          <t>24,85; 32,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,46; 31,22</t>
+          <t>17,01; 21,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,14; 37,27</t>
+          <t>30,27; 37,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,38; 30,83</t>
+          <t>25,02; 30,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,21; 30,93</t>
+          <t>25,28; 30,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,59; 28,55</t>
+          <t>17,27; 21,57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,89; 36,62</t>
+          <t>24,14; 35,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,86; 39,35</t>
+          <t>26,76; 39,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,96; 32,59</t>
+          <t>20,38; 32,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,38; 27,49</t>
+          <t>9,02; 25,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,23; 29,83</t>
+          <t>23,95; 29,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,0; 29,81</t>
+          <t>24,39; 30,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,12; 23,11</t>
+          <t>17,08; 22,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,01; 17,29</t>
+          <t>12,65; 18,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24,94; 30,18</t>
+          <t>25,19; 30,36</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,4; 30,6</t>
+          <t>25,48; 30,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,47; 23,69</t>
+          <t>18,65; 23,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,28; 18,42</t>
+          <t>12,39; 18,01</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,22; 34,03</t>
+          <t>30,27; 33,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,27; 31,77</t>
+          <t>28,28; 31,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,8; 29,53</t>
+          <t>25,74; 29,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,76; 20,06</t>
+          <t>17,82; 20,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,3; 33,84</t>
+          <t>30,34; 33,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,5; 30,8</t>
+          <t>27,47; 30,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,51; 27,85</t>
+          <t>24,57; 27,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,62; 19,89</t>
+          <t>17,04; 19,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,58; 33,33</t>
+          <t>30,72; 33,36</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,34; 30,81</t>
+          <t>28,34; 30,82</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25,61; 28,17</t>
+          <t>25,53; 28,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,22; 19,45</t>
+          <t>17,67; 19,6</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91995</t>
+          <t>93938</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76359</t>
+          <t>84482</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>168354</t>
+          <t>178420</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93279; 128128</t>
+          <t>95164; 131136</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>123268; 163485</t>
+          <t>123626; 164172</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77707; 113422</t>
+          <t>75095; 112236</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74778; 115441</t>
+          <t>75733; 114502</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>73680; 104395</t>
+          <t>71347; 102481</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63110; 96262</t>
+          <t>62874; 95290</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52303; 80774</t>
+          <t>51881; 80696</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62568; 90433</t>
+          <t>70649; 100015</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>177519; 224712</t>
+          <t>175547; 222356</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>197050; 248179</t>
+          <t>196080; 247866</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>137674; 182455</t>
+          <t>138428; 185451</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>146433; 192233</t>
+          <t>156626; 205461</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69218</t>
+          <t>74112</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62140</t>
+          <t>72876</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>131358</t>
+          <t>146989</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82905; 119286</t>
+          <t>84193; 117201</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89692; 126061</t>
+          <t>87891; 124505</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67927; 100441</t>
+          <t>66110; 99665</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54863; 89477</t>
+          <t>58577; 91597</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>106231; 140009</t>
+          <t>106739; 141944</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78795; 112508</t>
+          <t>79873; 112818</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79053; 114973</t>
+          <t>79245; 112963</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51641; 74503</t>
+          <t>60528; 85966</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>201349; 248752</t>
+          <t>200974; 248709</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>175011; 226065</t>
+          <t>176849; 227868</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>155611; 201740</t>
+          <t>155426; 202834</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>112600; 150767</t>
+          <t>126056; 171224</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89097</t>
+          <t>106751</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26919</t>
+          <t>32006</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>116016</t>
+          <t>138757</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>132615; 173369</t>
+          <t>133233; 171489</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>134999; 179991</t>
+          <t>136326; 181369</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102242; 139349</t>
+          <t>102875; 141790</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33651; 152128</t>
+          <t>87788; 128975</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34452; 56386</t>
+          <t>33756; 56020</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59470; 87806</t>
+          <t>58660; 88760</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26205; 46989</t>
+          <t>26892; 47659</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19590; 36371</t>
+          <t>23464; 42002</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>175401; 220530</t>
+          <t>175099; 220971</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>204684; 258337</t>
+          <t>204200; 254914</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134004; 177531</t>
+          <t>132930; 177707</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46563; 175060</t>
+          <t>115660; 160092</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>216799</t>
+          <t>223146</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>162098</t>
+          <t>180378</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>378897</t>
+          <t>403523</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>245222; 297669</t>
+          <t>245592; 298383</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>254076; 309384</t>
+          <t>251019; 310764</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>229201; 285998</t>
+          <t>229384; 287903</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>189653; 243919</t>
+          <t>196886; 254150</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>189387; 239076</t>
+          <t>190530; 237956</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>205020; 256503</t>
+          <t>204822; 254624</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>202197; 252827</t>
+          <t>202789; 252279</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>87087; 216223</t>
+          <t>160952; 201177</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>447324; 520573</t>
+          <t>448192; 520217</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>472236; 549121</t>
+          <t>464721; 548398</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>448221; 523279</t>
+          <t>447322; 524475</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>266191; 437854</t>
+          <t>367811; 438984</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79816</t>
+          <t>100286</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>167411</t>
+          <t>151323</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>247227</t>
+          <t>251609</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>67989; 96989</t>
+          <t>70413; 100190</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96604; 132908</t>
+          <t>95992; 131526</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96266; 132660</t>
+          <t>97894; 133675</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63361; 98077</t>
+          <t>82081; 123064</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>136110; 177003</t>
+          <t>136036; 175108</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>163463; 211783</t>
+          <t>162205; 209152</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>139270; 180803</t>
+          <t>138562; 182576</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>125730; 253907</t>
+          <t>134899; 171402</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>212221; 262348</t>
+          <t>213094; 263632</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>272358; 330846</t>
+          <t>268449; 330877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>247769; 303961</t>
+          <t>248447; 303988</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>207789; 357559</t>
+          <t>225020; 281039</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37370</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>109348</t>
+          <t>122111</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>146718</t>
+          <t>156841</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52821; 77719</t>
+          <t>51228; 76364</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>59170; 86691</t>
+          <t>58947; 87449</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50639; 78732</t>
+          <t>49232; 77693</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19451; 63818</t>
+          <t>20260; 57847</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>229120; 282085</t>
+          <t>226438; 282678</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>222334; 276224</t>
+          <t>225921; 278593</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>141266; 190744</t>
+          <t>140964; 188452</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>89347; 128645</t>
+          <t>103575; 148842</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>288798; 349448</t>
+          <t>291671; 351513</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>291302; 350945</t>
+          <t>292243; 352329</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>197042; 252752</t>
+          <t>198943; 254177</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>119852; 179740</t>
+          <t>129315; 187943</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>584294</t>
+          <t>632963</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>604276</t>
+          <t>643176</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1188570</t>
+          <t>1276139</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>739596; 832776</t>
+          <t>740815; 829991</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>822372; 924117</t>
+          <t>822558; 923567</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>685229; 784126</t>
+          <t>683661; 774512</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>450966; 657423</t>
+          <t>590543; 688310</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>830243; 927306</t>
+          <t>831156; 926507</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>863596; 967388</t>
+          <t>862571; 962929</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>699815; 795236</t>
+          <t>701538; 794197</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>511613; 695988</t>
+          <t>601988; 686313</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1586082; 1728662</t>
+          <t>1593723; 1730525</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1714398; 1863697</t>
+          <t>1714613; 1864592</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1411321; 1552632</t>
+          <t>1407180; 1543917</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1031265; 1318217</t>
+          <t>1209888; 1342295</t>
         </is>
       </c>
     </row>
